--- a/data/trans_orig/P36B08_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>479275</t>
+          <t>478908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>526638</t>
+          <t>525346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513869</t>
+          <t>513455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>555386</t>
+          <t>555254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1009956</t>
+          <t>1005945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1069019</t>
+          <t>1066790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167374</t>
+          <t>168666</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214737</t>
+          <t>215104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132965</t>
+          <t>133097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174482</t>
+          <t>174896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>313344</t>
+          <t>315573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372407</t>
+          <t>376418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>566696</t>
+          <t>569547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>625335</t>
+          <t>630257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>636283</t>
+          <t>631740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>694584</t>
+          <t>693756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1217613</t>
+          <t>1220195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1307838</t>
+          <t>1306024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336465</t>
+          <t>331543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395104</t>
+          <t>392253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272749</t>
+          <t>273577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331050</t>
+          <t>335593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621295</t>
+          <t>623109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711520</t>
+          <t>708938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>368063</t>
+          <t>367276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>420817</t>
+          <t>417648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>457074</t>
+          <t>459624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>504115</t>
+          <t>506621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>841050</t>
+          <t>841699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>912328</t>
+          <t>909353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257692</t>
+          <t>260861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310446</t>
+          <t>311233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179726</t>
+          <t>177220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>226767</t>
+          <t>224217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>450022</t>
+          <t>452997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>521300</t>
+          <t>520651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>548387</t>
+          <t>546313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>607610</t>
+          <t>605049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>687044</t>
+          <t>687543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>747333</t>
+          <t>746912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1253070</t>
+          <t>1255933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1337945</t>
+          <t>1339036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>333778</t>
+          <t>336339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>393001</t>
+          <t>395075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>291700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351568</t>
+          <t>351069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>642055</t>
+          <t>640964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726930</t>
+          <t>724067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2013745</t>
+          <t>2020508</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2128375</t>
+          <t>2125928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2341215</t>
+          <t>2344836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2449848</t>
+          <t>2451375</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4397999</t>
+          <t>4385114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4555090</t>
+          <t>4542259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1147334</t>
+          <t>1149781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1261964</t>
+          <t>1255201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>928289</t>
+          <t>926762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1036922</t>
+          <t>1033301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2098757</t>
+          <t>2111588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2255848</t>
+          <t>2268733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>506476</t>
+          <t>509983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>553239</t>
+          <t>555066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>551780</t>
+          <t>555349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>593775</t>
+          <t>595446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1076529</t>
+          <t>1075873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1137825</t>
+          <t>1140118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>147332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195922</t>
+          <t>192415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103275</t>
+          <t>101604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145270</t>
+          <t>141701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261623</t>
+          <t>259330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322919</t>
+          <t>323575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>687590</t>
+          <t>687982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>746587</t>
+          <t>748147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>766801</t>
+          <t>767422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>822099</t>
+          <t>822843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1471352</t>
+          <t>1468585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1554115</t>
+          <t>1552810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>267309</t>
+          <t>265749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326306</t>
+          <t>325914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207000</t>
+          <t>206256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262298</t>
+          <t>261677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488880</t>
+          <t>490185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>571643</t>
+          <t>574410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>471980</t>
+          <t>469940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>526914</t>
+          <t>524501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>552770</t>
+          <t>554095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>603311</t>
+          <t>605132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1038974</t>
+          <t>1039305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1117099</t>
+          <t>1114202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228624</t>
+          <t>231037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283558</t>
+          <t>285598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172802</t>
+          <t>170981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>223343</t>
+          <t>222018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414552</t>
+          <t>417449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>492677</t>
+          <t>492346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>657395</t>
+          <t>658229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>712519</t>
+          <t>715730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>847516</t>
+          <t>845566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>898912</t>
+          <t>896105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1518096</t>
+          <t>1521826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1593098</t>
+          <t>1596873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235220</t>
+          <t>232009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290344</t>
+          <t>289510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147303</t>
+          <t>150110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198699</t>
+          <t>200649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400856</t>
+          <t>397081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475858</t>
+          <t>472128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2376920</t>
+          <t>2378762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2486475</t>
+          <t>2487264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2772253</t>
+          <t>2770591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2868338</t>
+          <t>2869215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5181387</t>
+          <t>5183933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5330806</t>
+          <t>5328090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>933096</t>
+          <t>932307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1042651</t>
+          <t>1040809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680139</t>
+          <t>679262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>776224</t>
+          <t>777886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1637243</t>
+          <t>1639959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1786662</t>
+          <t>1784116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>474124</t>
+          <t>472883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>519635</t>
+          <t>521837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>485009</t>
+          <t>484529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>529148</t>
+          <t>527584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>968622</t>
+          <t>971145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1037002</t>
+          <t>1035567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151092</t>
+          <t>148890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196603</t>
+          <t>197844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140796</t>
+          <t>142360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184935</t>
+          <t>185415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303669</t>
+          <t>305104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372049</t>
+          <t>369526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>705329</t>
+          <t>703590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>764659</t>
+          <t>765651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>769328</t>
+          <t>770628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>825388</t>
+          <t>825948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1492545</t>
+          <t>1491741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1570760</t>
+          <t>1570648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>256686</t>
+          <t>255694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316016</t>
+          <t>317755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216432</t>
+          <t>215872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>272492</t>
+          <t>271192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492405</t>
+          <t>492517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>570620</t>
+          <t>571424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>471440</t>
+          <t>470501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>524767</t>
+          <t>526654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>542568</t>
+          <t>540583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>593612</t>
+          <t>593540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1026538</t>
+          <t>1030559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1102487</t>
+          <t>1104401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>224612</t>
+          <t>222725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277939</t>
+          <t>278878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184927</t>
+          <t>184999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235971</t>
+          <t>237956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425431</t>
+          <t>423517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>501380</t>
+          <t>497359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684311</t>
+          <t>682473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>736282</t>
+          <t>735084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>829611</t>
+          <t>832705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>879934</t>
+          <t>881146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1530736</t>
+          <t>1532710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1605396</t>
+          <t>1600732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199438</t>
+          <t>200636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251409</t>
+          <t>253247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157547</t>
+          <t>156335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207870</t>
+          <t>204776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367805</t>
+          <t>372469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>442465</t>
+          <t>440491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2389348</t>
+          <t>2392468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2491913</t>
+          <t>2498647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2683182</t>
+          <t>2676208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2780348</t>
+          <t>2778115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5097210</t>
+          <t>5092834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5246277</t>
+          <t>5239708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>885258</t>
+          <t>878524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>987823</t>
+          <t>984703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>747436</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>844602</t>
+          <t>851576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1658679</t>
+          <t>1665248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1807746</t>
+          <t>1812122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>601422</t>
+          <t>656036</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>583875</t>
+          <t>639348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>612637</t>
+          <t>666732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>647120</t>
+          <t>703056</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>637591</t>
+          <t>691987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>654766</t>
+          <t>711097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1248543</t>
+          <t>1359093</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1230393</t>
+          <t>1341398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1262524</t>
+          <t>1373087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59799</t>
+          <t>61757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77949</t>
+          <t>79452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633670</t>
+          <t>688859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674672</t>
+          <t>731990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308342</t>
+          <t>1420850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1145511</t>
+          <t>1000994</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1122759</t>
+          <t>983845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1168799</t>
+          <t>1014239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>928285</t>
+          <t>1039171</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>917999</t>
+          <t>1028473</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>936260</t>
+          <t>1048031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2073796</t>
+          <t>2040164</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2048503</t>
+          <t>2019255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2098684</t>
+          <t>2056696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46545</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>64068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38161</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>76523</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>59991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99713</t>
+          <t>97432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192056</t>
+          <t>1047913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956160</t>
+          <t>1068775</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148216</t>
+          <t>2116687</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>652569</t>
+          <t>747326</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>631176</t>
+          <t>728395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>667489</t>
+          <t>763769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>886008</t>
+          <t>762681</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>862880</t>
+          <t>743433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>912709</t>
+          <t>774809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1538576</t>
+          <t>1510007</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1505938</t>
+          <t>1484693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1571935</t>
+          <t>1530852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52111</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73504</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>49578</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>68826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>105325</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66111</t>
+          <t>84480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132108</t>
+          <t>130639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>864395</t>
+          <t>924895</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>844899</t>
+          <t>905046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>879199</t>
+          <t>939997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1046802</t>
+          <t>1067051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1031749</t>
+          <t>1052399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1058642</t>
+          <t>1079610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1911197</t>
+          <t>1991946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1887117</t>
+          <t>1970357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1931827</t>
+          <t>2011606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>50661</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35037</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61930</t>
+          <t>65313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>113989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87811</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132521</t>
+          <t>135578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925959</t>
+          <t>988224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093679</t>
+          <t>1117712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019638</t>
+          <t>2105935</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3225292</t>
+          <t>3298351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3308458</t>
+          <t>3361511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3481519</t>
+          <t>3547249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3538720</t>
+          <t>3595058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6717872</t>
+          <t>6856932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6824431</t>
+          <t>6937159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P36B08_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2023 (tasa de respuesta: 99,86%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
